--- a/data/smp_excel/계통한계가격_20260414_육지.xlsx
+++ b/data/smp_excel/계통한계가격_20260414_육지.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\과제_최종\data\smp_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A2B5B24-5DB3-4FFF-BA92-14E1EC5BB18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E0F227B-67AA-47DB-ACDD-1A820CB02953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3732" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{010DC85C-4CBA-425F-AEF5-B8008C19A25B}"/>
+    <workbookView xWindow="4080" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{2BF28A3A-CB1E-44F3-B31D-80A28554B49A}"/>
   </bookViews>
   <sheets>
     <sheet name="계통한계가격" sheetId="1" r:id="rId1"/>
@@ -130,11 +130,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="180" formatCode="#,###.#0"/>
-    <numFmt numFmtId="181" formatCode="#,##0_ "/>
+    <numFmt numFmtId="181" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="182" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="183" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +168,20 @@
       <name val="굴림"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF5357F9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFE84B00"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -237,7 +253,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -263,6 +279,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -578,7 +612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EAF12C-0042-4E28-855E-0466D61265C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE932958-4D06-46EF-AC4B-2507399A6327}">
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -599,7 +633,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>0</v>
+        <v>135.62</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -607,7 +641,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>0</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -615,155 +649,203 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>0</v>
+        <v>117.03</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6">
+        <v>126.24</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8"/>
+      <c r="B6" s="8">
+        <v>117.82</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8"/>
+      <c r="B7" s="8">
+        <v>106.79</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="8">
+        <v>106.79</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="8">
+        <v>106.79</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="9">
+        <v>109.6</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="8">
+        <v>114.93</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="8">
+        <v>122.91</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="8">
+        <v>125.52</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="8">
+        <v>111.54</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" s="8">
+        <v>99.09</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="8">
+        <v>99.07</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="8"/>
+      <c r="B17" s="8">
+        <v>99.05</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="8"/>
+      <c r="B18" s="11">
+        <v>99.03</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="8">
+        <v>110.56</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="8"/>
+      <c r="B20" s="12">
+        <v>118</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="8"/>
+      <c r="B21" s="8">
+        <v>120.51</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="8"/>
+      <c r="B22" s="8">
+        <v>122.91</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="8">
+        <v>135.59</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="8"/>
+      <c r="B24" s="14">
+        <v>135.62</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>125.84</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>125.63</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="8"/>
+      <c r="B27" s="8">
+        <v>127.13</v>
+      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="8"/>
+      <c r="B28" s="8">
+        <v>125.78</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
